--- a/processes/user_registration/input/users_to_invite.xlsx
+++ b/processes/user_registration/input/users_to_invite.xlsx
@@ -8,20 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alyona.Sachyova\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF274459-CF25-4661-849A-0221D225CDE2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4754CEEC-2A1E-41AD-96F9-50530C73D396}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16200" windowHeight="24705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Пользователи" sheetId="1" r:id="rId1"/>
     <sheet name="Инструкция" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="118">
   <si>
     <t>Фамилия</t>
   </si>
@@ -309,6 +309,72 @@
   </si>
   <si>
     <t>Талдыкорганский филиал</t>
+  </si>
+  <si>
+    <t>Тимкин</t>
+  </si>
+  <si>
+    <t>Андрей</t>
+  </si>
+  <si>
+    <t>Мусатаева</t>
+  </si>
+  <si>
+    <t>Айгерим</t>
+  </si>
+  <si>
+    <t>Сикымжанова</t>
+  </si>
+  <si>
+    <t>Дана</t>
+  </si>
+  <si>
+    <t>Тян</t>
+  </si>
+  <si>
+    <t>Владислав</t>
+  </si>
+  <si>
+    <t>Шалбаев</t>
+  </si>
+  <si>
+    <t>Марат</t>
+  </si>
+  <si>
+    <t>Салыкова</t>
+  </si>
+  <si>
+    <t>Асемгуль</t>
+  </si>
+  <si>
+    <t>Боровая</t>
+  </si>
+  <si>
+    <t>Юлия</t>
+  </si>
+  <si>
+    <t>Andrey.Timkin@theeurasia.kz</t>
+  </si>
+  <si>
+    <t>Aigerim.Mussatayeva@theeurasia.kz</t>
+  </si>
+  <si>
+    <t>Dana.Sikymzhanova@theeurasia.kz</t>
+  </si>
+  <si>
+    <t>Marat.Shalbayev@theeurasia.kz</t>
+  </si>
+  <si>
+    <t>Assemgul.Salykova@theeurasia.kz</t>
+  </si>
+  <si>
+    <t>Yuliya.Borovaya@theeurasia.kz</t>
+  </si>
+  <si>
+    <t>Vladislav.Tyan@theeurasia.kz</t>
+  </si>
+  <si>
+    <t>Филиалы</t>
   </si>
 </sst>
 </file>
@@ -417,7 +483,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -443,46 +509,12 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -644,7 +676,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultColWidth="20.125" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.375" bestFit="1" customWidth="1"/>
@@ -677,13 +709,13 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="E2" t="s">
         <v>91</v>
@@ -694,13 +726,13 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="E3" t="s">
         <v>91</v>
@@ -711,13 +743,13 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>100</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="E4" t="s">
         <v>91</v>
@@ -728,374 +760,75 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>105</v>
       </c>
       <c r="D5" t="s">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="E5" t="s">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9" t="s">
-        <v>72</v>
+      <c r="A6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D6" t="s">
+        <v>114</v>
       </c>
       <c r="E6" t="s">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>92</v>
+      <c r="A7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" t="s">
+        <v>115</v>
+      </c>
+      <c r="E7" t="s">
+        <v>117</v>
       </c>
       <c r="F7">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>92</v>
+      <c r="A8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E8" t="s">
+        <v>117</v>
       </c>
       <c r="F8">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="F9">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="F10">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="F11">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="F12">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="F13">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="F14">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="E16" t="s">
-        <v>91</v>
-      </c>
-      <c r="F16">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="E17" t="s">
-        <v>91</v>
-      </c>
-      <c r="F17">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="F18">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="F19">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="F20">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="F21">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="F22">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="F23">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="F24">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B6 B19 B23 A2:A5 A7:A18 A20:A22 A24">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D24">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C6 C19 C23">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
